--- a/memo/10-2025/input-changes-10-2025.xlsx
+++ b/memo/10-2025/input-changes-10-2025.xlsx
@@ -72,9 +72,6 @@
     <t xml:space="preserve">consumption_deflator</t>
   </si>
   <si>
-    <t xml:space="preserve">2023 Q2</t>
-  </si>
-  <si>
     <t xml:space="preserve">2023 Q3</t>
   </si>
   <si>
@@ -121,6 +118,9 @@
   </si>
   <si>
     <t xml:space="preserve">2027 Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 Q3</t>
   </si>
 </sst>
 </file>
@@ -523,22 +523,22 @@
         <v>19</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>1738.8</v>
+        <v>1784.4</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>2934.6</v>
+        <v>3005.4</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>2262.6</v>
+        <v>2282.4</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>4323.26885714286</v>
+        <v>4273.35036514286</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1927.1</v>
+        <v>1903.7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>512.087862857143</v>
+        <v>493.931086857143</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>0</v>
@@ -550,31 +550,31 @@
         <v>0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46.2453234375524</v>
+        <v>62.0712654345618</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>45</v>
+        <v>2.081508</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>327373</v>
+        <v>429322</v>
       </c>
       <c r="N2" s="1" t="n">
-        <v>19167</v>
+        <v>19936.3333333333</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>2.65920081020969</v>
+        <v>3.81474413527976</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>-2.92055019038152</v>
+        <v>6.86295145036153</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.855629570820793</v>
+        <v>0.141922652472348</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-2.22959113303005</v>
+        <v>5.59618472483887</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>2.99000483406797</v>
+        <v>2.71970977396323</v>
       </c>
     </row>
     <row r="3">
@@ -582,22 +582,22 @@
         <v>20</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>1784.4</v>
+        <v>1812</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>3005.4</v>
+        <v>3049</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>2282.4</v>
+        <v>2303.6</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>4273.35036514286</v>
+        <v>4269.165618</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1903.7</v>
+        <v>1911.3</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>493.931086857143</v>
+        <v>511.720086857143</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>0</v>
@@ -609,31 +609,31 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>62.0712654345618</v>
+        <v>68.3121900998493</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>2.081508</v>
+        <v>2.100618</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>331380</v>
+        <v>451322.666666667</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>19156</v>
+        <v>20095.6666666667</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>3.81474413527976</v>
+        <v>2.84364725966819</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>6.86295145036153</v>
+        <v>0.2857017697105</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.141922652472348</v>
+        <v>1.3158017114691</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>5.59618472483887</v>
+        <v>0.477506749015388</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>2.71970977396323</v>
+        <v>1.82057843338013</v>
       </c>
     </row>
     <row r="4">
@@ -641,22 +641,22 @@
         <v>21</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>1812</v>
+        <v>1834.3</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>3049</v>
+        <v>3097.5</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>2303.6</v>
+        <v>2343</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>4269.165618</v>
+        <v>4446.04653</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>1911.3</v>
+        <v>1978.5</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>511.720086857143</v>
+        <v>515.527086857143</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>0</v>
@@ -668,31 +668,31 @@
         <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>68.3121900998493</v>
+        <v>78.0145380046553</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>2.100618</v>
+        <v>2.58153</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>331492</v>
+        <v>455254</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>19193</v>
+        <v>20239.6666666667</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2.84364725966819</v>
+        <v>4.16921442287854</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.2857017697105</v>
+        <v>3.55975420469996</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1.3158017114691</v>
+        <v>1.77689345660519</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.477506749015388</v>
+        <v>3.21507472732108</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1.82057843338013</v>
+        <v>3.58834559038721</v>
       </c>
     </row>
     <row r="5">
@@ -700,22 +700,22 @@
         <v>22</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>1834.3</v>
+        <v>1867.5</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>3097.5</v>
+        <v>3127.6</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>2343</v>
+        <v>2383.8</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>4446.04653</v>
+        <v>4522.569045</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>1978.5</v>
+        <v>2022.9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>515.527086857143</v>
+        <v>524.750251857143</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0</v>
@@ -727,31 +727,31 @@
         <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>78.0145380046553</v>
+        <v>85.4387215838714</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>2.58153</v>
+        <v>2.604045</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>334244</v>
+        <v>457983.666666667</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>19178</v>
+        <v>20321.3333333333</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>4.16921442287854</v>
+        <v>3.06789494231547</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>3.55975420469996</v>
+        <v>1.13251009679061</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1.77689345660519</v>
+        <v>0.994669624259203</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>3.21507472732108</v>
+        <v>1.1035661065375</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>3.58834559038721</v>
+        <v>2.59206026542906</v>
       </c>
     </row>
     <row r="6">
@@ -759,22 +759,22 @@
         <v>23</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1867.5</v>
+        <v>1917.9</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>3127.6</v>
+        <v>3169.1</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>2383.8</v>
+        <v>2423.4</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>4522.569045</v>
+        <v>4589.591465</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>2022.9</v>
+        <v>2059.8</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>524.750251857143</v>
+        <v>546.479472857143</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>0</v>
@@ -786,31 +786,31 @@
         <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>85.4387215838714</v>
+        <v>79.6290028317487</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>2.604045</v>
+        <v>2.626465</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>338416</v>
+        <v>467739</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>19167</v>
+        <v>20423.3333333333</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>3.06789494231547</v>
+        <v>2.42026283990759</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>1.13251009679061</v>
+        <v>1.57994395283227</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.994669624259203</v>
+        <v>2.62977198232084</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>1.1035661065375</v>
+        <v>1.77267955564631</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>2.59206026542906</v>
+        <v>1.69941764671198</v>
       </c>
     </row>
     <row r="7">
@@ -818,22 +818,22 @@
         <v>24</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>1917.9</v>
+        <v>1950</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>3169.1</v>
+        <v>3200.8</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>2423.4</v>
+        <v>2462.8</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>4589.591465</v>
+        <v>4655.148835</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>2059.8</v>
+        <v>2101</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>546.479472857143</v>
+        <v>552.787468557143</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0</v>
@@ -845,31 +845,31 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>79.6290028317487</v>
+        <v>71.1791672183253</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.626465</v>
+        <v>2.649835</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>339417</v>
+        <v>471235</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>19173</v>
+        <v>20519.6666666666</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>2.42026283990759</v>
+        <v>2.40898298285142</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>1.57994395283227</v>
+        <v>1.31794961593215</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>2.62977198232084</v>
+        <v>1.4168785751552</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>1.77267955564631</v>
+        <v>1.33694986261501</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>1.69941764671198</v>
+        <v>2.51839708422128</v>
       </c>
     </row>
     <row r="8">
@@ -877,22 +877,22 @@
         <v>25</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>1950</v>
+        <v>1949.7</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>3200.8</v>
+        <v>3245.8</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>2462.8</v>
+        <v>2538.3</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>4655.148835</v>
+        <v>4794.444442</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>2101</v>
+        <v>2127.8</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>552.787468557143</v>
+        <v>514.421139857143</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>0</v>
@@ -904,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>71.1791672183253</v>
+        <v>73.9806362924226</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>2.649835</v>
+        <v>2.645442</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>345062</v>
+        <v>468903.333333333</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>19212</v>
+        <v>20588</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>2.40898298285142</v>
+        <v>5.86627785528204</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1.31794961593215</v>
+        <v>4.02082630394835</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1.4168785751552</v>
+        <v>2.67569727671195</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>1.33694986261501</v>
+        <v>3.76072597280368</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>2.51839708422128</v>
+        <v>3.43051694846648</v>
       </c>
     </row>
     <row r="9">
@@ -936,58 +936,58 @@
         <v>26</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>1949.7</v>
+        <v>1956.4</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>3245.8</v>
+        <v>3280.6</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2538.3</v>
+        <v>2579.6</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>4794.444442</v>
+        <v>4973.6686</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>2127.8</v>
+        <v>2196.8</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>514.421139857143</v>
+        <v>486.521762357143</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>73.9806362924226</v>
+        <v>88.3944428040623</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>2.645442</v>
+        <v>2.6696</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>339178</v>
+        <v>475718.666666667</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>19240</v>
+        <v>20631.6666666666</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>5.86627785528204</v>
+        <v>7.00705346466592</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>4.02082630394835</v>
+        <v>0.947484063996984</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>2.67569727671195</v>
+        <v>2.19139117742579</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>3.76072597280368</v>
+        <v>1.18575780248784</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>3.43051694846648</v>
+        <v>2.13199307045904</v>
       </c>
     </row>
     <row r="10">
@@ -995,22 +995,22 @@
         <v>27</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>1956.4</v>
+        <v>1979.74532893704</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>3280.6</v>
+        <v>3310.58125327749</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>2579.6</v>
+        <v>2476.40237828624</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>4973.6686</v>
+        <v>5005.45981573521</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>2196.8</v>
+        <v>2250.47533286928</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>486.521762357143</v>
+        <v>489.125119360448</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>-0.3</v>
@@ -1022,31 +1022,27 @@
         <v>-0.3</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>88.3944428040623</v>
+        <v>103.083510693309</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>2.6696</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>342484</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>19272</v>
-      </c>
+        <v>-8.306994</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
       <c r="O10" s="2" t="n">
-        <v>7.00705346466592</v>
+        <v>0.002966870309562</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0.947484063996984</v>
+        <v>3.13438683522629</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>2.19139117742579</v>
+        <v>3.13438683522629</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>1.18575780248784</v>
+        <v>3.13438683522629</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>2.13199307045904</v>
+        <v>3.21749320145084</v>
       </c>
     </row>
     <row r="11">
@@ -1054,22 +1050,22 @@
         <v>28</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1979.74532893704</v>
+        <v>2006.76290286156</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>3310.58125327749</v>
+        <v>3341.68181349335</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>2476.40237828624</v>
+        <v>2488.69259383739</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>5005.45981573521</v>
+        <v>5041.39165487405</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>2250.47533286928</v>
+        <v>2289.58548426295</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>489.125119360448</v>
+        <v>487.868429381336</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>-0.3</v>
@@ -1081,27 +1077,27 @@
         <v>-0.3</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>103.083510693309</v>
+        <v>109.658761987664</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>-8.306994</v>
+        <v>-8.28246</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="2" t="n">
-        <v>0.002966870309562</v>
+        <v>2.41196036148992</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>3.13438683522629</v>
+        <v>3.23943548052301</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>3.13438683522629</v>
+        <v>3.23943548052301</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>3.13438683522629</v>
+        <v>3.23943548052301</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>3.21749320145084</v>
+        <v>2.60113929386974</v>
       </c>
     </row>
     <row r="12">
@@ -1109,34 +1105,34 @@
         <v>29</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>2006.76290286156</v>
+        <v>2051.1056274537</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>3341.68181349335</v>
+        <v>3373.66737243847</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>2488.69259383739</v>
+        <v>2468.99984893768</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>5041.39165487405</v>
+        <v>5143.47441605237</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>2289.58548426295</v>
+        <v>2329.45465615017</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>487.868429381336</v>
+        <v>490.64948408791</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>-0.3</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.24</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>109.658761987664</v>
+        <v>134.709036355557</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>-8.28246</v>
@@ -1144,19 +1140,19 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="2" t="n">
-        <v>2.41196036148992</v>
+        <v>2.15156026172931</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>3.23943548052301</v>
+        <v>3.31646376298169</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>3.23943548052301</v>
+        <v>3.31646376298169</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>3.23943548052301</v>
+        <v>3.31646376298169</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>2.60113929386974</v>
+        <v>2.24691319446388</v>
       </c>
     </row>
     <row r="13">
@@ -1164,34 +1160,34 @@
         <v>30</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>2051.1056274537</v>
+        <v>2076.17476099563</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>3373.66737243847</v>
+        <v>3403.4892424388</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>2468.99984893768</v>
+        <v>2481.25332624221</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>5143.47441605237</v>
+        <v>5203.22030836988</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>2329.45465615017</v>
+        <v>2370.05200179332</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>490.64948408791</v>
+        <v>490.654941657143</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I13" s="1" t="n">
         <v>0.06</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>-0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>134.709036355557</v>
+        <v>155.206844624839</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>-8.28246</v>
@@ -1199,19 +1195,19 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="2" t="n">
-        <v>2.15156026172931</v>
+        <v>2.27908500071972</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>3.31646376298169</v>
+        <v>3.14257138985898</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>3.31646376298169</v>
+        <v>3.14257138985898</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>3.31646376298169</v>
+        <v>3.14257138985898</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>2.24691319446388</v>
+        <v>2.13779577824049</v>
       </c>
     </row>
     <row r="14">
@@ -1219,22 +1215,22 @@
         <v>31</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>2076.17476099563</v>
+        <v>2096.66663787088</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>3403.4892424388</v>
+        <v>3433.8730194392</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>2481.25332624221</v>
+        <v>2493.56761671613</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>5203.22030836988</v>
+        <v>5262.78400638154</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>2370.05200179332</v>
+        <v>2411.39135585736</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>490.654941657143</v>
+        <v>494.491072100581</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>-0.2</v>
@@ -1246,27 +1242,27 @@
         <v>-0.14</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>155.206844624839</v>
+        <v>162.820344255939</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>-8.28246</v>
+        <v>-11</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="2" t="n">
-        <v>2.27908500071972</v>
+        <v>2.32632952071579</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>3.14257138985898</v>
+        <v>3.10130534191213</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>3.14257138985898</v>
+        <v>3.10130534191213</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>3.14257138985898</v>
+        <v>3.10130534191213</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>2.13779577824049</v>
+        <v>2.13131956877191</v>
       </c>
     </row>
     <row r="15">
@@ -1274,22 +1270,22 @@
         <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>2096.66663787088</v>
+        <v>2110.02889238115</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>3433.8730194392</v>
+        <v>3463.52454615578</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>2493.56761671613</v>
+        <v>2505.94302217105</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>5262.78400638154</v>
+        <v>5293.59869882381</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>2411.39135585736</v>
+        <v>2429.3530529951</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>494.491072100581</v>
+        <v>496.355148090304</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>-0.2</v>
@@ -1301,7 +1297,7 @@
         <v>-0.14</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>162.820344255939</v>
+        <v>160.445027356869</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>-11</v>
@@ -1309,19 +1305,19 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="2" t="n">
-        <v>2.32632952071579</v>
+        <v>2.38896858747151</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>3.10130534191213</v>
+        <v>3.10153987564559</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>3.10130534191213</v>
+        <v>3.10153987564559</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>3.10130534191213</v>
+        <v>3.10153987564559</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>2.13131956877191</v>
+        <v>2.14111741577905</v>
       </c>
     </row>
     <row r="16">
@@ -1329,34 +1325,34 @@
         <v>33</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>2110.02889238115</v>
+        <v>2128.26272610237</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>3463.52454615578</v>
+        <v>3492.52886324142</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2505.94302217105</v>
+        <v>2625.92185078075</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>5293.59869882381</v>
+        <v>5391.1823188095</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>2429.3530529951</v>
+        <v>2466.03583573082</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>496.355148090304</v>
+        <v>499.247444985141</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>0.06</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>-0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>160.445027356869</v>
+        <v>146.435353395161</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>-11</v>
@@ -1364,19 +1360,19 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="2" t="n">
-        <v>2.38896858747151</v>
+        <v>2.24125556014079</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>3.10153987564559</v>
+        <v>3.05422694255624</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>3.10153987564559</v>
+        <v>3.05422694255624</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>3.10153987564559</v>
+        <v>3.05422694255624</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>2.14111741577905</v>
+        <v>2.02786517583231</v>
       </c>
     </row>
     <row r="17">
@@ -1384,22 +1380,22 @@
         <v>34</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>2128.26272610237</v>
+        <v>2142.62433392647</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>3492.52886324142</v>
+        <v>3522.3379634022</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2625.92185078075</v>
+        <v>2638.95412124276</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>5391.1823188095</v>
+        <v>5450.56158665791</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>2466.03583573082</v>
+        <v>2503.27252181734</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>499.247444985141</v>
+        <v>502.168240857143</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>-0.1</v>
@@ -1411,7 +1407,7 @@
         <v>-0.04</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>146.435353395161</v>
+        <v>123.274912601363</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>-11</v>
@@ -1419,19 +1415,19 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="2" t="n">
-        <v>2.24125556014079</v>
+        <v>2.21473201084055</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>3.05422694255624</v>
+        <v>3.03346798788409</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>3.05422694255624</v>
+        <v>3.03346798788409</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>3.05422694255624</v>
+        <v>3.03346798788409</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>2.02786517583231</v>
+        <v>2.01818315150002</v>
       </c>
     </row>
     <row r="18">
@@ -1439,54 +1435,48 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>2142.62433392647</v>
+        <v>0</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>3522.3379634022</v>
+        <v>0</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>2638.95412124276</v>
+        <v>2652.05106997131</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>5450.56158665791</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>2503.27252181734</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>502.168240857143</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>-0.04</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
       <c r="K18" s="1" t="n">
-        <v>123.274912601363</v>
+        <v>0</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="2" t="n">
-        <v>2.21473201084055</v>
+        <v>2.27723026141111</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>3.03346798788409</v>
+        <v>2.99945580576912</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>3.03346798788409</v>
+        <v>2.99945580576912</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>3.03346798788409</v>
+        <v>2.99945580576912</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>2.01818315150002</v>
+        <v>2.00874890479379</v>
       </c>
     </row>
   </sheetData>
@@ -1587,22 +1577,22 @@
         <v>20</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>45.6000000000001</v>
+        <v>27.5999999999999</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>70.8000000000002</v>
+        <v>43.5999999999999</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>19.8000000000002</v>
+        <v>21.1999999999998</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-49.9184920000007</v>
+        <v>-4.1847471428573</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>-23.3999999999999</v>
+        <v>7.59999999999991</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>-18.156776</v>
+        <v>17.7889999999999</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>0</v>
@@ -1614,31 +1604,31 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>15.8259419970094</v>
+        <v>6.24092466528752</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>-42.918492</v>
+        <v>0.0191100000000004</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>4007</v>
+        <v>22000.666666667</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>-11</v>
+        <v>159.333333333343</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1.15554332507006</v>
+        <v>-0.971096875611566</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>9.78350164074305</v>
+        <v>-6.57724968065103</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.713706918348445</v>
+        <v>1.17387905899675</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>7.82577585786892</v>
+        <v>-5.11867797582348</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>-0.270295060104742</v>
+        <v>-0.899131340583104</v>
       </c>
     </row>
     <row r="4">
@@ -1646,22 +1636,22 @@
         <v>21</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>27.5999999999999</v>
+        <v>22.3</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>43.5999999999999</v>
+        <v>48.5</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>21.1999999999998</v>
+        <v>39.4000000000001</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>-4.1847471428573</v>
+        <v>176.880911999999</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>7.59999999999991</v>
+        <v>67.2</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>17.7889999999999</v>
+        <v>3.80700000000019</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>0</v>
@@ -1673,31 +1663,31 @@
         <v>0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>6.24092466528752</v>
+        <v>9.70234790480593</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>0.0191100000000004</v>
+        <v>0.480912</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>112</v>
+        <v>3931.33333333302</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-0.971096875611566</v>
+        <v>1.32556716321035</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-6.57724968065103</v>
+        <v>3.27405243498946</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1.17387905899675</v>
+        <v>0.461091745136089</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-5.11867797582348</v>
+        <v>2.73756797830569</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>-0.899131340583104</v>
+        <v>1.76776715700708</v>
       </c>
     </row>
     <row r="5">
@@ -1705,22 +1695,22 @@
         <v>22</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>22.3</v>
+        <v>33.2</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>48.5</v>
+        <v>30.0999999999999</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>39.4000000000001</v>
+        <v>40.8000000000002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>176.880911999999</v>
+        <v>76.5225150000015</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>67.2</v>
+        <v>44.4000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>3.80700000000019</v>
+        <v>9.22316499999988</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0</v>
@@ -1732,31 +1722,31 @@
         <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>9.70234790480593</v>
+        <v>7.42418357921616</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>0.480912</v>
+        <v>0.0225149999999998</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>2752</v>
+        <v>2729.66666666698</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>-15</v>
+        <v>81.666666666657</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.32556716321035</v>
+        <v>-1.10131948056307</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>3.27405243498946</v>
+        <v>-2.42724410790935</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.461091745136089</v>
+        <v>-0.782223832345985</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>2.73756797830569</v>
+        <v>-2.11150862078358</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1.76776715700708</v>
+        <v>-0.996285324958146</v>
       </c>
     </row>
     <row r="6">
@@ -1764,22 +1754,22 @@
         <v>23</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>33.2</v>
+        <v>50.4000000000001</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>30.0999999999999</v>
+        <v>41.5</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>40.8000000000002</v>
+        <v>39.5999999999999</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>76.5225150000015</v>
+        <v>67.0224199999984</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44.4000000000001</v>
+        <v>36.9000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>9.22316499999988</v>
+        <v>21.7292210000002</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>0</v>
@@ -1791,31 +1781,31 @@
         <v>0</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>7.42418357921616</v>
+        <v>-5.80971875212276</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>0.0225149999999998</v>
+        <v>0.0224199999999999</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>4172</v>
+        <v>9755.33333333302</v>
       </c>
       <c r="N6" s="1" t="n">
-        <v>-11</v>
+        <v>101.999999999971</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-1.10131948056307</v>
+        <v>-0.64763210240788</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-2.42724410790935</v>
+        <v>0.447433856041668</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.782223832345985</v>
+        <v>1.63510235806164</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-2.11150862078358</v>
+        <v>0.669113449108805</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>-0.996285324958146</v>
+        <v>-0.892642618717088</v>
       </c>
     </row>
     <row r="7">
@@ -1823,22 +1813,22 @@
         <v>24</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>50.4000000000001</v>
+        <v>32.0999999999999</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>41.5</v>
+        <v>31.7000000000003</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>39.5999999999999</v>
+        <v>39.4000000000001</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>67.0224199999984</v>
+        <v>65.5573700000014</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>36.9000000000001</v>
+        <v>41.1999999999998</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>21.7292210000002</v>
+        <v>6.30799569999965</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0</v>
@@ -1850,31 +1840,31 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>-5.80971875212276</v>
+        <v>-8.44983561342336</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>0.0224199999999999</v>
+        <v>0.0233699999999999</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>1001</v>
+        <v>3496</v>
       </c>
       <c r="N7" s="1" t="n">
-        <v>6</v>
+        <v>96.3333333333285</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.64763210240788</v>
+        <v>-0.011279857056179</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.447433856041668</v>
+        <v>-0.261994336900129</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>1.63510235806164</v>
+        <v>-1.21289340716564</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.669113449108805</v>
+        <v>-0.435729693031295</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>-0.892642618717088</v>
+        <v>0.818979437509304</v>
       </c>
     </row>
     <row r="8">
@@ -1882,22 +1872,22 @@
         <v>25</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>32.0999999999999</v>
+        <v>-0.299999999999955</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>31.7000000000003</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>39.4000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>65.5573700000014</v>
+        <v>139.295607000001</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>41.1999999999998</v>
+        <v>26.8000000000002</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>6.30799569999965</v>
+        <v>-38.3663286999998</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>0</v>
@@ -1909,31 +1899,31 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>-8.44983561342336</v>
+        <v>2.80146907409727</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>0.0233699999999999</v>
+        <v>-0.00439299999999987</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>5645</v>
+        <v>-2331.66666666698</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>39</v>
+        <v>68.333333333343</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-0.011279857056179</v>
+        <v>3.45729487243063</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.261994336900129</v>
+        <v>2.70287668801621</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-1.21289340716564</v>
+        <v>1.25881870155675</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.435729693031295</v>
+        <v>2.42377611018867</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>0.818979437509304</v>
+        <v>0.912119864245198</v>
       </c>
     </row>
     <row r="9">
@@ -1941,58 +1931,58 @@
         <v>26</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>-0.299999999999955</v>
+        <v>6.70000000000005</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45</v>
+        <v>34.7999999999997</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>75.5</v>
+        <v>41.2999999999997</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>139.295607000001</v>
+        <v>179.224157999999</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>26.8000000000002</v>
+        <v>68.9999999999995</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-38.3663286999998</v>
+        <v>-27.8993775000001</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>2.80146907409727</v>
+        <v>14.4138065116397</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>-0.00439299999999987</v>
+        <v>0.0241579999999999</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>-5884</v>
+        <v>6815.33333333395</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>28</v>
+        <v>43.666666666657</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>3.45729487243063</v>
+        <v>1.14077560938388</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2.70287668801621</v>
+        <v>-3.07334223995137</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>1.25881870155675</v>
+        <v>-0.484306099286158</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>2.42377611018867</v>
+        <v>-2.57496817031584</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0.912119864245198</v>
+        <v>-1.29852387800744</v>
       </c>
     </row>
     <row r="10">
@@ -2000,58 +1990,54 @@
         <v>27</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>6.70000000000005</v>
+        <v>23.3453289370386</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>34.7999999999997</v>
+        <v>29.9812532774904</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>41.2999999999997</v>
+        <v>-103.197621713764</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>179.224157999999</v>
+        <v>31.7912157352148</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>68.9999999999995</v>
+        <v>53.6753328692816</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-27.8993775000001</v>
+        <v>2.60335700330575</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>14.4138065116397</v>
+        <v>14.6890678892471</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>0.0241579999999999</v>
-      </c>
-      <c r="M10" s="1" t="n">
-        <v>3306</v>
-      </c>
-      <c r="N10" s="1" t="n">
-        <v>32</v>
-      </c>
+        <v>-10.976594</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
       <c r="O10" s="2" t="n">
-        <v>1.14077560938388</v>
+        <v>-7.00408659435636</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>-3.07334223995137</v>
+        <v>2.1869027712293</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.484306099286158</v>
+        <v>0.942995657800494</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-2.57496817031584</v>
+        <v>1.94862903273845</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>-1.29852387800744</v>
+        <v>1.0855001309918</v>
       </c>
     </row>
     <row r="11">
@@ -2059,22 +2045,22 @@
         <v>28</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>23.3453289370386</v>
+        <v>27.0175739245187</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>29.9812532774904</v>
+        <v>31.1005602158616</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>-103.197621713764</v>
+        <v>12.2902155511538</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>31.7912157352148</v>
+        <v>35.9318391388324</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>53.6753328692816</v>
+        <v>39.1101513936642</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>2.60335700330575</v>
+        <v>-1.25668997911237</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>0</v>
@@ -2086,27 +2072,27 @@
         <v>0</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>14.6890678892471</v>
+        <v>6.57525129435452</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>-10.976594</v>
+        <v>0.0245339999999992</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="2" t="n">
-        <v>-7.00408659435636</v>
+        <v>2.40899349118036</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>2.1869027712293</v>
+        <v>0.105048645296724</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>0.942995657800494</v>
+        <v>0.105048645296724</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>1.94862903273845</v>
+        <v>0.105048645296724</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>1.0855001309918</v>
+        <v>-0.616353907581102</v>
       </c>
     </row>
     <row r="12">
@@ -2114,54 +2100,54 @@
         <v>29</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>27.0175739245187</v>
+        <v>44.3427245921466</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>31.1005602158616</v>
+        <v>31.9855589451217</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>12.2902155511538</v>
+        <v>-19.692744899708</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>35.9318391388324</v>
+        <v>102.082761178322</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>39.1101513936642</v>
+        <v>39.8691718872233</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-1.25668997911237</v>
+        <v>2.78105470657397</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>6.57525129435452</v>
+        <v>25.0502743678927</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>0.0245339999999992</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="2" t="n">
-        <v>2.40899349118036</v>
+        <v>-0.260400099760605</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0.105048645296724</v>
+        <v>0.0770282824586799</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>0.105048645296724</v>
+        <v>0.0770282824586799</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>0.105048645296724</v>
+        <v>0.0770282824586799</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>-0.616353907581102</v>
+        <v>-0.354226099405852</v>
       </c>
     </row>
     <row r="13">
@@ -2169,34 +2155,34 @@
         <v>30</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>44.3427245921466</v>
+        <v>25.0691335419265</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>31.9855589451217</v>
+        <v>29.8218700003254</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>-19.692744899708</v>
+        <v>12.2534773045281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>102.082761178322</v>
+        <v>59.7458923175145</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>39.8691718872233</v>
+        <v>40.5973456431493</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>2.78105470657397</v>
+        <v>0.00545756923270346</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>25.0502743678927</v>
+        <v>20.4978082692824</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>0</v>
@@ -2204,19 +2190,19 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="2" t="n">
-        <v>-0.260400099760605</v>
+        <v>0.127524738990403</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0.0770282824586799</v>
+        <v>-0.173892373122708</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.0770282824586799</v>
+        <v>-0.173892373122708</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>0.0770282824586799</v>
+        <v>-0.173892373122708</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>-0.354226099405852</v>
+        <v>-0.109117416223392</v>
       </c>
     </row>
     <row r="14">
@@ -2224,54 +2210,54 @@
         <v>31</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>25.0691335419265</v>
+        <v>20.4918768752523</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>29.8218700003254</v>
+        <v>30.3837770004056</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>12.2534773045281</v>
+        <v>12.3142904739243</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>59.7458923175145</v>
+        <v>59.5636980116515</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>40.5973456431493</v>
+        <v>41.3393540640445</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.00545756923270346</v>
+        <v>3.83613044343792</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>20.4978082692824</v>
+        <v>7.6134996310999</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>0</v>
+        <v>-2.71754</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="2" t="n">
-        <v>0.127524738990403</v>
+        <v>0.0472445199960703</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>-0.173892373122708</v>
+        <v>-0.041266047946853</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>-0.173892373122708</v>
+        <v>-0.041266047946853</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>-0.173892373122708</v>
+        <v>-0.041266047946853</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>-0.109117416223392</v>
+        <v>-0.00647620946858662</v>
       </c>
     </row>
     <row r="15">
@@ -2279,22 +2265,22 @@
         <v>32</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>20.4918768752523</v>
+        <v>13.362254510263</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>30.3837770004056</v>
+        <v>29.6515267165723</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>12.3142904739243</v>
+        <v>12.375405454919</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>59.5636980116515</v>
+        <v>30.8146924422708</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>41.3393540640445</v>
+        <v>17.961697137735</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>3.83613044343792</v>
+        <v>1.86407598972312</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>0</v>
@@ -2306,27 +2292,27 @@
         <v>0</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>7.6134996310999</v>
+        <v>-2.37531689907016</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>-2.71754</v>
+        <v>0</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="2" t="n">
-        <v>0.0472445199960703</v>
+        <v>0.0626390667557208</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>-0.041266047946853</v>
+        <v>0.000234533733456388</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>-0.041266047946853</v>
+        <v>0.000234533733456388</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>-0.041266047946853</v>
+        <v>0.000234533733456388</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>-0.00647620946858662</v>
+        <v>0.00979784700714248</v>
       </c>
     </row>
     <row r="16">
@@ -2334,34 +2320,34 @@
         <v>33</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>13.362254510263</v>
+        <v>18.2338337212291</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>29.6515267165723</v>
+        <v>29.0043170856416</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>12.375405454919</v>
+        <v>119.978828609701</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>30.8146924422708</v>
+        <v>97.5836199856922</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>17.961697137735</v>
+        <v>36.6827827357179</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>1.86407598972312</v>
+        <v>2.89229689483693</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>-2.37531689907016</v>
+        <v>-14.0096739617076</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>0</v>
@@ -2369,19 +2355,19 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="2" t="n">
-        <v>0.0626390667557208</v>
+        <v>-0.14771302733072</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>0.000234533733456388</v>
+        <v>-0.0473129330893496</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>0.000234533733456388</v>
+        <v>-0.0473129330893496</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>0.000234533733456388</v>
+        <v>-0.0473129330893496</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>0.00979784700714248</v>
+        <v>-0.113252239946737</v>
       </c>
     </row>
     <row r="17">
@@ -2389,34 +2375,34 @@
         <v>34</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>18.2338337212291</v>
+        <v>14.3616078240907</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>29.0043170856416</v>
+        <v>29.8091001607791</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>119.978828609701</v>
+        <v>13.0322704620057</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>97.5836199856922</v>
+        <v>59.3792678484097</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>36.6827827357179</v>
+        <v>37.2366860865263</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>2.89229689483693</v>
+        <v>2.92079587200203</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>-14.0096739617076</v>
+        <v>-23.1604407937979</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>0</v>
@@ -2424,19 +2410,19 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="2" t="n">
-        <v>-0.14771302733072</v>
+        <v>-0.0265235493002391</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>-0.0473129330893496</v>
+        <v>-0.0207589546721509</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>-0.0473129330893496</v>
+        <v>-0.0207589546721509</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>-0.0473129330893496</v>
+        <v>-0.0207589546721509</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>-0.113252239946737</v>
+        <v>-0.00968202433229148</v>
       </c>
     </row>
     <row r="18">
@@ -2444,54 +2430,48 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>14.3616078240907</v>
+        <v>-2142.62433392647</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>29.8091001607791</v>
+        <v>-3522.3379634022</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>13.0322704620057</v>
+        <v>13.096948728552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>59.3792678484097</v>
+        <v>-5450.56158665791</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>37.2366860865263</v>
+        <v>-2503.27252181734</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>2.92079587200203</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>0</v>
-      </c>
+        <v>-502.168240857143</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
       <c r="K18" s="1" t="n">
-        <v>-23.1604407937979</v>
+        <v>-123.274912601363</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="2" t="n">
-        <v>-0.0265235493002391</v>
+        <v>0.062498250570564</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>-0.0207589546721509</v>
+        <v>-0.0340121821149619</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>-0.0207589546721509</v>
+        <v>-0.0340121821149619</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>-0.0207589546721509</v>
+        <v>-0.0340121821149619</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>-0.00968202433229148</v>
+        <v>-0.00943424670623028</v>
       </c>
     </row>
   </sheetData>
